--- a/Info/INKR Values.xlsx
+++ b/Info/INKR Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbewe\RetroComputing\AmstradCPC\MyHardware\Amstrad-CPC-IO-Logger\Amstrad-CPC-IO-Logger\Info\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{015CF0F2-97A7-4EAB-8A3A-0319D53914A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F5B512-42A2-410C-870A-96FB30B00AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8E7BEA5C-DDB8-4B5F-A008-538991E6F30A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
@@ -371,7 +371,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Color</t>
   </si>
@@ -503,13 +503,25 @@
   </si>
   <si>
     <t>Hex (wo 010)</t>
+  </si>
+  <si>
+    <t>Default GA Pen</t>
+  </si>
+  <si>
+    <t>1 and 14</t>
+  </si>
+  <si>
+    <t>11 and 15</t>
+  </si>
+  <si>
+    <t>0 and BORDER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -537,6 +549,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -558,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -574,6 +592,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -596,16 +623,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>581025</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>285750</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>161925</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -620,7 +647,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4105275" y="762000"/>
+          <a:off x="5286375" y="561975"/>
           <a:ext cx="4419600" cy="2752725"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1365,17 +1392,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6F657EA-C383-45C2-8AC4-645BBD35B174}">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1388,7 +1416,7 @@
       <c r="D1" s="5"/>
       <c r="E1" s="5"/>
     </row>
-    <row r="2" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1402,8 +1430,11 @@
       <c r="E2" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F2" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -1421,8 +1452,11 @@
         <f>BIN2HEX(RIGHT(D3,5))</f>
         <v>14</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F3" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
@@ -1440,8 +1474,11 @@
         <f t="shared" ref="E4:E35" si="1">BIN2HEX(RIGHT(D4,5))</f>
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F4" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
@@ -1459,8 +1496,11 @@
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F5" s="8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
@@ -1478,8 +1518,9 @@
         <f t="shared" si="1"/>
         <v>1C</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
@@ -1497,8 +1538,9 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
@@ -1516,8 +1558,9 @@
         <f t="shared" si="1"/>
         <v>1D</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
@@ -1535,8 +1578,11 @@
         <f t="shared" si="1"/>
         <v>C</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F9" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
@@ -1554,8 +1600,9 @@
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
@@ -1573,8 +1620,11 @@
         <f t="shared" si="1"/>
         <v>D</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F11" s="8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="e" vm="10">
         <v>#VALUE!</v>
       </c>
@@ -1592,8 +1642,9 @@
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="e" vm="11">
         <v>#VALUE!</v>
       </c>
@@ -1611,8 +1662,11 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F13" s="8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="e" vm="12">
         <v>#VALUE!</v>
       </c>
@@ -1630,8 +1684,9 @@
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="e" vm="13">
         <v>#VALUE!</v>
       </c>
@@ -1649,8 +1704,11 @@
         <f t="shared" si="1"/>
         <v>1E</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F15" s="8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="e" vm="14">
         <v>#VALUE!</v>
       </c>
@@ -1668,8 +1726,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="e" vm="15">
         <v>#VALUE!</v>
       </c>
@@ -1687,8 +1746,11 @@
         <f t="shared" si="1"/>
         <v>1F</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F17" s="8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="e" vm="16">
         <v>#VALUE!</v>
       </c>
@@ -1706,8 +1768,9 @@
         <f t="shared" si="1"/>
         <v>E</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="e" vm="17">
         <v>#VALUE!</v>
       </c>
@@ -1725,8 +1788,11 @@
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F19" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="e" vm="18">
         <v>#VALUE!</v>
       </c>
@@ -1744,8 +1810,9 @@
         <f t="shared" si="1"/>
         <v>F</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F20" s="8"/>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="e" vm="19">
         <v>#VALUE!</v>
       </c>
@@ -1763,8 +1830,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F21" s="8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="e" vm="20">
         <v>#VALUE!</v>
       </c>
@@ -1782,8 +1852,9 @@
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F22" s="8"/>
+    </row>
+    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="e" vm="21">
         <v>#VALUE!</v>
       </c>
@@ -1801,8 +1872,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="e" vm="22">
         <v>#VALUE!</v>
       </c>
@@ -1820,8 +1894,9 @@
         <f t="shared" si="1"/>
         <v>1A</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F24" s="8"/>
+    </row>
+    <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="e" vm="23">
         <v>#VALUE!</v>
       </c>
@@ -1839,8 +1914,11 @@
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F25" s="8">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="e" vm="24">
         <v>#VALUE!</v>
       </c>
@@ -1858,8 +1936,9 @@
         <f t="shared" si="1"/>
         <v>1B</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="e" vm="25">
         <v>#VALUE!</v>
       </c>
@@ -1877,8 +1956,11 @@
         <f>BIN2HEX(RIGHT(D27,5))</f>
         <v>A</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F27" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="e" vm="26">
         <v>#VALUE!</v>
       </c>
@@ -1896,8 +1978,9 @@
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F28" s="8"/>
+    </row>
+    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="e" vm="27">
         <v>#VALUE!</v>
       </c>
@@ -1915,15 +1998,18 @@
         <f t="shared" si="1"/>
         <v>B</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F29" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="e" vm="28">
         <v>#VALUE!</v>
       </c>
@@ -1942,7 +2028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="e" vm="29">
         <v>#VALUE!</v>
       </c>
@@ -1961,7 +2047,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="e" vm="30">
         <v>#VALUE!</v>
       </c>
@@ -1999,7 +2085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="e" vm="32">
         <v>#VALUE!</v>
       </c>
